--- a/data/fob_kalkulation.xlsx
+++ b/data/fob_kalkulation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,40 +479,45 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ek_fob_euro</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>produktionszeit</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>kubikmeter</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>lcl</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>container_20</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>container_40hc</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>zollsatz</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sonder_toolingkosten</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>archiv</t>
         </is>
@@ -570,27 +575,298 @@
         <v>954.25</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>30</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>192</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>0.025</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BD12A8B0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>234567</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Stuhl</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Testlieferant</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>650</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>13325479</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kühlbox</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>asdj</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>145</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>800</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>25808973</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kühlbox</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>asdasd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>145</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>160</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>450</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>98031F65</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kühlbox</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>asd</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>145</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>145</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>800</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
         <v>0</v>
       </c>
     </row>
